--- a/InputData/bldgs/SoBRCBbG/Shr of Blgd Rtrft Cost Borne by Govt.xlsx
+++ b/InputData/bldgs/SoBRCBbG/Shr of Blgd Rtrft Cost Borne by Govt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff-nonadmin\CodeRepositories\eps-us\InputData\bldgs\SoBRCBbG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\SoBRCBbG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{107AC2A6-81B2-4E9B-8126-021B7368DEC8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A7A7DE-DA23-49E1-A5E1-8348D3BFC51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="75" windowWidth="24090" windowHeight="14700" xr2:uid="{B7370FBA-4486-4F99-AF7A-4FA274821588}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{B7370FBA-4486-4F99-AF7A-4FA274821588}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>SoBRCBbG Share of Building Retrofit Costs Borne by Government</t>
   </si>
@@ -80,6 +82,15 @@
   </si>
   <si>
     <t>Government Cost Share</t>
+  </si>
+  <si>
+    <t>data centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. They copy the commercial value so it is defined; the retrofit program does not apply to data centers.</t>
   </si>
 </sst>
 </file>
@@ -140,7 +151,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -148,6 +159,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -167,9 +181,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -207,7 +221,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -313,7 +327,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -455,7 +469,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -463,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01810828-2E37-43FF-9A71-F4460C03E7FB}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -517,6 +531,14 @@
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="285" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +555,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" customWidth="1"/>
@@ -571,6 +593,15 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
